--- a/data_processed/results_OLS_kg_CO2e_per_capitatenure.xlsx
+++ b/data_processed/results_OLS_kg_CO2e_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6248" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6535" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12511.73282751714</v>
+        <v>11351.13238419626</v>
       </c>
       <c r="D2" t="n">
-        <v>1.202517589886586e-183</v>
+        <v>8.446255632710018e-171</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1093.100226964367</v>
+        <v>-960.6978299242261</v>
       </c>
       <c r="D3" t="n">
-        <v>3.357629572838663e-180</v>
+        <v>1.939574308586473e-143</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-493.5162087841978</v>
+        <v>-2042.055126293592</v>
       </c>
       <c r="D4" t="n">
-        <v>3.032116758439213e-52</v>
+        <v>7.629200515612839e-181</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.80271199002795</v>
+        <v>27.57030868248186</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2556290817061561</v>
+        <v>5.809800527645302e-31</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-141.6425035033062</v>
+        <v>-716.0253297690449</v>
       </c>
       <c r="D6" t="n">
-        <v>6.525408128307854e-09</v>
+        <v>3.155266546596053e-107</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0324103367949057</v>
+        <v>-23.80284155521245</v>
       </c>
       <c r="D7" t="n">
-        <v>2.320884084746571e-11</v>
+        <v>0.1832825112032852</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.112329309328961</v>
+        <v>-106.4277896703537</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1478360444824413</v>
+        <v>3.894477947811548e-05</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_train</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2628.890531464669</v>
+        <v>0.01659217892630614</v>
       </c>
       <c r="D9" t="n">
-        <v>1.628097631489967e-297</v>
+        <v>0.00134174608534247</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.9202370952186</v>
+        <v>0.3549444082970606</v>
       </c>
       <c r="D10" t="n">
-        <v>3.404568170774922e-06</v>
+        <v>1.269466821506179e-06</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +595,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>districtheating_pc</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-5.276274510325827</v>
+        <v>-1166.312694111089</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2683918916111352</v>
+        <v>0.000797884401207553</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>heatpump_pc</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>102.2379421239897</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.622973120572658</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>solarcapacity</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-599.7178947965007</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.556015078482474e-37</v>
       </c>
     </row>
   </sheetData>
